--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1888.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1888.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\@downloads\ugvi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049B21BA-85BA-4392-9C6E-82E27A185EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFDFFC7-B0BA-4153-9F01-D7A1C1DA5F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="check" sheetId="2" r:id="rId2"/>
     <sheet name="notes" sheetId="3" r:id="rId3"/>
+    <sheet name="исправления" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="153">
   <si>
     <t>губ</t>
   </si>
@@ -464,13 +465,43 @@
   </si>
   <si>
     <t>v-diff</t>
+  </si>
+  <si>
+    <t>чс</t>
+  </si>
+  <si>
+    <t>Для Волынской губернии сумма уездов чн:</t>
+  </si>
+  <si>
+    <t>разница</t>
+  </si>
+  <si>
+    <t>сумма</t>
+  </si>
+  <si>
+    <t>напечатано</t>
+  </si>
+  <si>
+    <t>чр</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подольская </t>
+  </si>
+  <si>
+    <t>г. Николаев</t>
+  </si>
+  <si>
+    <t>г. Одесса</t>
+  </si>
+  <si>
+    <t>Сахалин</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -480,14 +511,21 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -497,11 +535,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0F766E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2E8F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -525,6 +558,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -538,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -549,12 +594,24 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,7 +630,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ExtractedData" displayName="ExtractedData" ref="A1:D99">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ExtractedData" displayName="ExtractedData" ref="A1:D102">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="губ"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="чж NYY"/>
@@ -753,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:T102"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -779,29 +836,29 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="3"/>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
+      <c r="A2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="14">
         <v>346371</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="14">
         <v>12733</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="14">
         <v>8018</v>
       </c>
       <c r="F2" s="3"/>
@@ -813,16 +870,16 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
+      <c r="A3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="14">
         <v>833276</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="14">
         <v>26860</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="14">
         <v>19429</v>
       </c>
       <c r="F3" s="3"/>
@@ -834,16 +891,16 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
+      <c r="A4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="14">
         <v>1309304</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="14">
         <v>54761</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="14">
         <v>33408</v>
       </c>
       <c r="F4" s="3"/>
@@ -855,16 +912,16 @@
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
+      <c r="A5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="19">
         <v>1319304</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="13">
         <v>55587</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="13">
         <v>32912</v>
       </c>
       <c r="F5" s="3"/>
@@ -876,16 +933,16 @@
       <c r="L5" s="3"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
+      <c r="A6" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>2303602</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="14">
         <v>119051</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="14">
         <v>80316</v>
       </c>
       <c r="F6" s="3"/>
@@ -918,16 +975,16 @@
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
+      <c r="A8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="14">
         <v>2995133</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="14">
         <v>157321</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="14">
         <v>95868</v>
       </c>
       <c r="F8" s="3"/>
@@ -939,16 +996,16 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
+      <c r="A9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="14">
         <v>1554752</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="14">
         <v>54319</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="14">
         <v>35604</v>
       </c>
       <c r="F9" s="3"/>
@@ -960,16 +1017,16 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
+      <c r="A10" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="14">
         <v>1712274</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="14">
         <v>75862</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="14">
         <v>45253</v>
       </c>
       <c r="F10" s="3"/>
@@ -981,16 +1038,16 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
+      <c r="A11" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="14">
         <v>1326468</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="14">
         <v>69060</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="14">
         <v>33339</v>
       </c>
       <c r="F11" s="3"/>
@@ -1002,16 +1059,16 @@
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" t="s">
+      <c r="A12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="14">
         <v>1337913</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="14">
         <v>81236</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="14">
         <v>49862</v>
       </c>
       <c r="F12" s="3"/>
@@ -1029,10 +1086,10 @@
       <c r="B13" s="3">
         <v>2500435</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="6">
         <v>124380</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="6">
         <v>81485</v>
       </c>
       <c r="F13" s="3"/>
@@ -1044,40 +1101,40 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="5">
-        <v>18868326</v>
-      </c>
-      <c r="C14" s="5">
+      <c r="B14" s="17">
+        <v>18858326</v>
+      </c>
+      <c r="C14" s="17">
         <v>887317</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="17">
         <v>553285</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="9">
         <f>SUM(B2:B13)</f>
         <v>18868326</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="9">
         <f>SUM(C2:C13)</f>
         <v>887317</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="9">
         <f>SUM(D2:D13)</f>
         <v>553285</v>
       </c>
       <c r="I14" s="3"/>
-      <c r="J14" s="11">
+      <c r="J14" s="9">
         <f>ExtractedData[[#This Row],[чж NYY]]-F14</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="11">
+        <v>-10000</v>
+      </c>
+      <c r="K14" s="9">
         <f>ExtractedData[[#This Row],[чр YY]]-G14</f>
         <v>0</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="9">
         <f>ExtractedData[[#This Row],[чу YY]]-H14</f>
         <v>0</v>
       </c>
@@ -1104,16 +1161,16 @@
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="20">
         <v>444514</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>17569</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="5">
         <v>11042</v>
       </c>
       <c r="F16" s="3"/>
@@ -1146,16 +1203,16 @@
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" t="s">
+      <c r="A18" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="14">
         <v>706860</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="14">
         <v>29051</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="14">
         <v>15256</v>
       </c>
       <c r="F18" s="3"/>
@@ -1167,16 +1224,16 @@
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
+      <c r="A19" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="19">
         <v>611795</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="14">
         <v>24364</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="14">
         <v>17620</v>
       </c>
       <c r="F19" s="3"/>
@@ -1188,16 +1245,16 @@
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
+      <c r="A20" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="19">
         <v>1064900</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="14">
         <v>40623</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="14">
         <v>25914</v>
       </c>
       <c r="F20" s="3"/>
@@ -1209,16 +1266,16 @@
       <c r="L20" s="3"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" t="s">
+      <c r="A21" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="19">
         <v>1146665</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="14">
         <v>44246</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="14">
         <v>25356</v>
       </c>
       <c r="F21" s="3"/>
@@ -1230,16 +1287,16 @@
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" t="s">
+      <c r="A22" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="19">
         <v>612323</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="14">
         <v>24445</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="14">
         <v>14339</v>
       </c>
       <c r="F22" s="3"/>
@@ -1251,16 +1308,16 @@
       <c r="L22" s="3"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" t="s">
+      <c r="A23" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="14">
         <v>742032</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="14">
         <v>30815</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="14">
         <v>16922</v>
       </c>
       <c r="F23" s="3"/>
@@ -1272,16 +1329,16 @@
       <c r="L23" s="3"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" t="s">
+      <c r="A24" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="19">
         <v>638317</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="14">
         <v>21370</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="14">
         <v>16295</v>
       </c>
       <c r="F24" s="3"/>
@@ -1293,16 +1350,16 @@
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
+      <c r="A25" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="19">
         <v>630659</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="14">
         <v>25198</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="14">
         <v>16813</v>
       </c>
       <c r="F25" s="3"/>
@@ -1314,16 +1371,16 @@
       <c r="L25" s="3"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" t="s">
+      <c r="A26" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="14">
         <v>688953</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="14">
         <v>17877</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="14">
         <v>12570</v>
       </c>
       <c r="F26" s="3"/>
@@ -1335,16 +1392,16 @@
       <c r="L26" s="3"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" t="s">
+      <c r="A27" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="19">
         <v>1239750</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="14">
         <v>36395</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="14">
         <v>26105</v>
       </c>
       <c r="F27" s="3"/>
@@ -1356,16 +1413,16 @@
       <c r="L27" s="3"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" t="s">
+      <c r="A28" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="14">
         <v>396785</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="14">
         <v>11809</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="14">
         <v>9200</v>
       </c>
       <c r="F28" s="3"/>
@@ -1377,55 +1434,55 @@
       <c r="L28" s="3"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="17">
         <v>10838913</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="17">
         <v>399713</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="17">
         <v>255575</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="9">
         <f>SUM(B15:B28)</f>
         <v>10798570</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="9">
         <f>SUM(C15:C28)</f>
         <v>399713</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="9">
         <f>SUM(D15:D28)</f>
         <v>255535</v>
       </c>
       <c r="I29" s="3"/>
-      <c r="J29" s="11">
+      <c r="J29" s="9">
         <f>ExtractedData[[#This Row],[чж NYY]]-F29</f>
         <v>40343</v>
       </c>
-      <c r="K29" s="11">
+      <c r="K29" s="9">
         <f>ExtractedData[[#This Row],[чр YY]]-G29</f>
         <v>0</v>
       </c>
-      <c r="L29" s="11">
+      <c r="L29" s="9">
         <f>ExtractedData[[#This Row],[чу YY]]-H29</f>
         <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
+      <c r="A30" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="14">
         <v>1525804</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="14">
         <v>73064</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="14">
         <v>43634</v>
       </c>
       <c r="F30" s="3"/>
@@ -1437,16 +1494,16 @@
       <c r="L30" s="3"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" t="s">
+      <c r="A31" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="14">
         <v>1434942</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="14">
         <v>79540</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="14">
         <v>54191</v>
       </c>
       <c r="F31" s="3"/>
@@ -1458,16 +1515,16 @@
       <c r="L31" s="3"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" t="s">
+      <c r="A32" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="19">
         <v>1255715</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="14">
         <v>54974</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="14">
         <v>36533</v>
       </c>
       <c r="F32" s="3"/>
@@ -1479,16 +1536,16 @@
       <c r="L32" s="3"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" t="s">
+      <c r="A33" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="14">
         <v>2650756</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="14">
         <v>139267</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="14">
         <v>89062</v>
       </c>
       <c r="F33" s="3"/>
@@ -1500,16 +1557,16 @@
       <c r="L33" s="3"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" t="s">
+      <c r="A34" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="14">
         <v>2924015</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="14">
         <v>153745</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="14">
         <v>101070</v>
       </c>
       <c r="F34" s="3"/>
@@ -1521,16 +1578,16 @@
       <c r="L34" s="3"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" t="s">
+      <c r="A35" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="19">
         <v>1587275</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="14">
         <v>92193</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="14">
         <v>49502</v>
       </c>
       <c r="F35" s="3"/>
@@ -1542,16 +1599,16 @@
       <c r="L35" s="3"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" t="s">
+      <c r="A36" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="14">
         <v>2149445</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="14">
         <v>104595</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="14">
         <v>69104</v>
       </c>
       <c r="F36" s="3"/>
@@ -1563,16 +1620,16 @@
       <c r="L36" s="3"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" t="s">
+      <c r="A37" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="14">
         <v>1221377</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="14">
         <v>59313</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="14">
         <v>38318</v>
       </c>
       <c r="F37" s="3"/>
@@ -1584,16 +1641,16 @@
       <c r="L37" s="3"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" t="s">
+      <c r="A38" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="14">
         <v>1367905</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="14">
         <v>64132</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="14">
         <v>50244</v>
       </c>
       <c r="F38" s="3"/>
@@ -1626,16 +1683,16 @@
       <c r="L39" s="3"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="5">
         <v>779410</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="5">
         <v>33557</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="5">
         <v>27696</v>
       </c>
       <c r="F40" s="3"/>
@@ -1668,16 +1725,16 @@
       <c r="L41" s="3"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" t="s">
+      <c r="A42" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="14">
         <v>1523529</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="14">
         <v>85519</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="14">
         <v>69216</v>
       </c>
       <c r="F42" s="3"/>
@@ -1689,16 +1746,16 @@
       <c r="L42" s="3"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" t="s">
+      <c r="A43" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="14">
         <v>1240665</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="14">
         <v>58415</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="14">
         <v>36752</v>
       </c>
       <c r="F43" s="3"/>
@@ -1710,16 +1767,16 @@
       <c r="L43" s="3"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" t="s">
+      <c r="A44" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="14">
         <v>345283</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="14">
         <v>16797</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="14">
         <v>12080</v>
       </c>
       <c r="F44" s="3"/>
@@ -1731,16 +1788,16 @@
       <c r="L44" s="3"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" t="s">
+      <c r="A45" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="14">
         <v>2071964</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="14">
         <v>105526</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="14">
         <v>67264</v>
       </c>
       <c r="F45" s="3"/>
@@ -1752,16 +1809,16 @@
       <c r="L45" s="3"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" t="s">
+      <c r="A46" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="14">
         <v>1543427</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="14">
         <v>83960</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="14">
         <v>59613</v>
       </c>
       <c r="F46" s="3"/>
@@ -1773,16 +1830,16 @@
       <c r="L46" s="3"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" t="s">
+      <c r="A47" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="14">
         <v>2742514</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="14">
         <v>155758</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="14">
         <v>110142</v>
       </c>
       <c r="F47" s="3"/>
@@ -1794,16 +1851,16 @@
       <c r="L47" s="3"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" t="s">
+      <c r="A48" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="14">
         <v>2848307</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="14">
         <v>133410</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="14">
         <v>75641</v>
       </c>
       <c r="F48" s="3"/>
@@ -1814,17 +1871,17 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" t="s">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="19">
         <v>980152</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="14">
         <v>50752</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="14">
         <v>32852</v>
       </c>
       <c r="F49" s="3"/>
@@ -1835,17 +1892,17 @@
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" t="s">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="14">
         <v>1876581</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="14">
         <v>94003</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="14">
         <v>60567</v>
       </c>
       <c r="F50" s="3"/>
@@ -1856,17 +1913,17 @@
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" t="s">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51" s="14">
         <v>2570800</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="14">
         <v>154751</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51" s="14">
         <v>101773</v>
       </c>
       <c r="F51" s="3"/>
@@ -1877,17 +1934,17 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="6" t="s">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="17">
         <v>867607</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C52" s="17">
         <v>27199</v>
       </c>
-      <c r="D52" s="7">
+      <c r="D52" s="17">
         <v>26033</v>
       </c>
       <c r="F52" s="3"/>
@@ -1898,17 +1955,17 @@
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" t="s">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53" s="14">
         <v>824129</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="14">
         <v>39246</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="14">
         <v>25048</v>
       </c>
       <c r="F53" s="3"/>
@@ -1919,17 +1976,17 @@
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" t="s">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="14">
         <v>2351077</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="14">
         <v>126534</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="14">
         <v>86678</v>
       </c>
       <c r="F54" s="3"/>
@@ -1940,17 +1997,17 @@
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" t="s">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55" s="14">
         <v>1605335</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="14">
         <v>80877</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D55" s="14">
         <v>54493</v>
       </c>
       <c r="F55" s="3"/>
@@ -1961,17 +2018,17 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" t="s">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="14">
         <v>1358756</v>
       </c>
-      <c r="C56" s="3">
+      <c r="C56" s="14">
         <v>78652</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56" s="14">
         <v>49496</v>
       </c>
       <c r="F56" s="3"/>
@@ -1982,17 +2039,17 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" t="s">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57" s="14">
         <v>1104314</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="14">
         <v>54265</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="14">
         <v>35313</v>
       </c>
       <c r="F57" s="3"/>
@@ -2003,17 +2060,17 @@
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" t="s">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="19">
         <v>2782155</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="14">
         <v>141051</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="14">
         <v>89139</v>
       </c>
       <c r="F58" s="3"/>
@@ -2024,17 +2081,17 @@
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" t="s">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="19">
         <v>1313681</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="14">
         <v>86639</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="14">
         <v>54869</v>
       </c>
       <c r="F59" s="3"/>
@@ -2044,18 +2101,21 @@
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" t="s">
+      <c r="R59" s="3"/>
+      <c r="S59" s="3"/>
+      <c r="T59" s="3"/>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="14">
         <v>1475183</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="14">
         <v>76217</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="14">
         <v>51590</v>
       </c>
       <c r="F60" s="3"/>
@@ -2065,18 +2125,21 @@
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" t="s">
+      <c r="R60" s="3"/>
+      <c r="S60" s="3"/>
+      <c r="T60" s="3"/>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="14">
         <v>1980301</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="14">
         <v>96158</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61" s="14">
         <v>63512</v>
       </c>
       <c r="F61" s="3"/>
@@ -2087,17 +2150,17 @@
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" t="s">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62" s="19">
         <v>2366557</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62" s="14">
         <v>123618</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="14">
         <v>76772</v>
       </c>
       <c r="F62" s="3"/>
@@ -2108,17 +2171,17 @@
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" t="s">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B63" s="14">
         <v>1792163</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="14">
         <v>101170</v>
       </c>
-      <c r="D63" s="3">
+      <c r="D63" s="14">
         <v>57900</v>
       </c>
       <c r="F63" s="3"/>
@@ -2129,18 +2192,18 @@
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" t="s">
-        <v>66</v>
-      </c>
-      <c r="B64" s="3">
-        <v>2174352</v>
-      </c>
-      <c r="C64" s="3">
-        <v>109530</v>
-      </c>
-      <c r="D64" s="3">
-        <v>64974</v>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B64" s="14">
+        <v>73694</v>
+      </c>
+      <c r="C64" s="14">
+        <v>3178</v>
+      </c>
+      <c r="D64" s="14">
+        <v>2473</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
@@ -2149,19 +2212,22 @@
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3"/>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>151</v>
       </c>
       <c r="B65" s="3">
-        <v>1149452</v>
+        <v>274209</v>
       </c>
       <c r="C65" s="3">
-        <v>46434</v>
+        <v>10500</v>
       </c>
       <c r="D65" s="3">
-        <v>31671</v>
+        <v>7459</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
@@ -2170,58 +2236,43 @@
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B66" s="5">
-        <v>62629449</v>
-      </c>
-      <c r="C66" s="5">
-        <v>3176386</v>
-      </c>
-      <c r="D66" s="5">
-        <v>2084554</v>
-      </c>
-      <c r="F66" s="11">
-        <f>SUM(B30:B65)</f>
-        <v>61777887</v>
-      </c>
-      <c r="G66" s="11">
-        <f>SUM(C30:C65)</f>
-        <v>3171854</v>
-      </c>
-      <c r="H66" s="11">
-        <f>SUM(D30:D65)</f>
-        <v>2078270</v>
-      </c>
+      <c r="Q65" s="3"/>
+      <c r="R65" s="3"/>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B66" s="14">
+        <v>2174352</v>
+      </c>
+      <c r="C66" s="14">
+        <v>109530</v>
+      </c>
+      <c r="D66" s="14">
+        <v>64974</v>
+      </c>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
       <c r="I66" s="3"/>
-      <c r="J66" s="11">
-        <f>ExtractedData[[#This Row],[чж NYY]]-F66</f>
-        <v>851562</v>
-      </c>
-      <c r="K66" s="11">
-        <f>ExtractedData[[#This Row],[чр YY]]-G66</f>
-        <v>4532</v>
-      </c>
-      <c r="L66" s="11">
-        <f>ExtractedData[[#This Row],[чу YY]]-H66</f>
-        <v>6284</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B67" s="7">
-        <v>1962369</v>
-      </c>
-      <c r="C67" s="7">
-        <v>147277</v>
-      </c>
-      <c r="D67" s="7">
-        <v>67072</v>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67" s="14">
+        <v>1149452</v>
+      </c>
+      <c r="C67" s="14">
+        <v>46434</v>
+      </c>
+      <c r="D67" s="14">
+        <v>31671</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
@@ -2231,57 +2282,57 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B68" s="5">
-        <v>94289057</v>
-      </c>
-      <c r="C68" s="5">
-        <v>4579693</v>
-      </c>
-      <c r="D68" s="5">
-        <v>2960486</v>
-      </c>
-      <c r="F68" s="11">
-        <f>SUM(F3:F67)</f>
-        <v>91444783</v>
-      </c>
-      <c r="G68" s="11">
-        <f>SUM(G3:G67)</f>
-        <v>4458884</v>
-      </c>
-      <c r="H68" s="11">
-        <f>SUM(H3:H67)</f>
-        <v>2887090</v>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B68" s="17">
+        <v>62629449</v>
+      </c>
+      <c r="C68" s="17">
+        <v>3176386</v>
+      </c>
+      <c r="D68" s="17">
+        <v>2084554</v>
+      </c>
+      <c r="F68" s="9">
+        <f>SUM(B30:B67)</f>
+        <v>62125790</v>
+      </c>
+      <c r="G68" s="9">
+        <f>SUM(C30:C67)</f>
+        <v>3185532</v>
+      </c>
+      <c r="H68" s="9">
+        <f>SUM(D30:D67)</f>
+        <v>2088202</v>
       </c>
       <c r="I68" s="3"/>
-      <c r="J68" s="11">
+      <c r="J68" s="9">
         <f>ExtractedData[[#This Row],[чж NYY]]-F68</f>
-        <v>2844274</v>
-      </c>
-      <c r="K68" s="11">
+        <v>503659</v>
+      </c>
+      <c r="K68" s="9">
         <f>ExtractedData[[#This Row],[чр YY]]-G68</f>
-        <v>120809</v>
-      </c>
-      <c r="L68" s="11">
+        <v>-9146</v>
+      </c>
+      <c r="L68" s="9">
         <f>ExtractedData[[#This Row],[чу YY]]-H68</f>
-        <v>73396</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" t="s">
-        <v>71</v>
-      </c>
-      <c r="B69" s="3">
-        <v>749089</v>
-      </c>
-      <c r="C69" s="3">
-        <v>19110</v>
-      </c>
-      <c r="D69" s="3">
-        <v>16636</v>
+        <v>-3648</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" s="17">
+        <v>1962369</v>
+      </c>
+      <c r="C69" s="17">
+        <v>147277</v>
+      </c>
+      <c r="D69" s="17">
+        <v>67072</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
@@ -2291,39 +2342,57 @@
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" t="s">
-        <v>72</v>
-      </c>
-      <c r="B70" s="3">
-        <v>601987</v>
-      </c>
-      <c r="C70" s="3">
-        <v>13574</v>
-      </c>
-      <c r="D70" s="3">
-        <v>13378</v>
-      </c>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70" s="17">
+        <v>94289057</v>
+      </c>
+      <c r="C70" s="17">
+        <v>4579693</v>
+      </c>
+      <c r="D70" s="17">
+        <v>2960486</v>
+      </c>
+      <c r="F70" s="9">
+        <f>SUM(F3:F69)</f>
+        <v>91792686</v>
+      </c>
+      <c r="G70" s="9">
+        <f>SUM(G3:G69)</f>
+        <v>4472562</v>
+      </c>
+      <c r="H70" s="9">
+        <f>SUM(H3:H69)</f>
+        <v>2897022</v>
+      </c>
       <c r="I70" s="3"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" t="s">
-        <v>73</v>
-      </c>
-      <c r="B71" s="3">
-        <v>755226</v>
-      </c>
-      <c r="C71" s="3">
-        <v>19719</v>
-      </c>
-      <c r="D71" s="3">
-        <v>14961</v>
+      <c r="J70" s="9">
+        <f>ExtractedData[[#This Row],[чж NYY]]-F70</f>
+        <v>2496371</v>
+      </c>
+      <c r="K70" s="9">
+        <f>ExtractedData[[#This Row],[чр YY]]-G70</f>
+        <v>107131</v>
+      </c>
+      <c r="L70" s="9">
+        <f>ExtractedData[[#This Row],[чу YY]]-H70</f>
+        <v>63464</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" s="14">
+        <v>749089</v>
+      </c>
+      <c r="C71" s="14">
+        <v>19110</v>
+      </c>
+      <c r="D71" s="14">
+        <v>16636</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
@@ -2333,18 +2402,18 @@
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" t="s">
-        <v>74</v>
-      </c>
-      <c r="B72" s="3">
-        <v>237114</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>75</v>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B72" s="14">
+        <v>601987</v>
+      </c>
+      <c r="C72" s="14">
+        <v>13574</v>
+      </c>
+      <c r="D72" s="14">
+        <v>13378</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
@@ -2354,18 +2423,18 @@
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" t="s">
-        <v>76</v>
-      </c>
-      <c r="B73" s="3">
-        <v>1350054</v>
-      </c>
-      <c r="C73" s="3">
-        <v>83293</v>
-      </c>
-      <c r="D73" s="3">
-        <v>52845</v>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B73" s="14">
+        <v>755226</v>
+      </c>
+      <c r="C73" s="14">
+        <v>19719</v>
+      </c>
+      <c r="D73" s="14">
+        <v>14961</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
@@ -2375,18 +2444,18 @@
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" t="s">
-        <v>77</v>
-      </c>
-      <c r="B74" s="3">
-        <v>959715</v>
-      </c>
-      <c r="C74" s="3">
-        <v>26825</v>
-      </c>
-      <c r="D74" s="3">
-        <v>13075</v>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B74" s="14">
+        <v>237114</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>75</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
@@ -2396,18 +2465,18 @@
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" t="s">
-        <v>78</v>
-      </c>
-      <c r="B75" s="3">
-        <v>670648</v>
-      </c>
-      <c r="C75" s="3">
-        <v>43139</v>
-      </c>
-      <c r="D75" s="3">
-        <v>24945</v>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75" s="14">
+        <v>1350054</v>
+      </c>
+      <c r="C75" s="14">
+        <v>83293</v>
+      </c>
+      <c r="D75" s="14">
+        <v>52845</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
@@ -2417,18 +2486,18 @@
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" t="s">
-        <v>79</v>
-      </c>
-      <c r="B76" s="3">
-        <v>705616</v>
-      </c>
-      <c r="C76" s="3">
-        <v>22719</v>
-      </c>
-      <c r="D76" s="3">
-        <v>16794</v>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" s="14">
+        <v>959715</v>
+      </c>
+      <c r="C76" s="14">
+        <v>26825</v>
+      </c>
+      <c r="D76" s="14">
+        <v>13075</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
@@ -2438,18 +2507,18 @@
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" t="s">
-        <v>80</v>
-      </c>
-      <c r="B77" s="3">
-        <v>823537</v>
-      </c>
-      <c r="C77" s="3">
-        <v>28629</v>
-      </c>
-      <c r="D77" s="3">
-        <v>15520</v>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77" s="14">
+        <v>670648</v>
+      </c>
+      <c r="C77" s="14">
+        <v>43139</v>
+      </c>
+      <c r="D77" s="14">
+        <v>24945</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
@@ -2459,18 +2528,18 @@
       <c r="K77" s="3"/>
       <c r="L77" s="3"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" t="s">
-        <v>81</v>
-      </c>
-      <c r="B78" s="3">
-        <v>677491</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>75</v>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" s="14">
+        <v>705616</v>
+      </c>
+      <c r="C78" s="14">
+        <v>22719</v>
+      </c>
+      <c r="D78" s="14">
+        <v>16794</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
@@ -2480,56 +2549,38 @@
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B79" s="5">
-        <v>7839177</v>
-      </c>
-      <c r="C79" s="5">
-        <v>257306</v>
-      </c>
-      <c r="D79" s="5">
-        <v>168154</v>
-      </c>
-      <c r="F79" s="11">
-        <f>SUM(B69:B78)</f>
-        <v>7530477</v>
-      </c>
-      <c r="G79" s="11">
-        <f>SUM(C69:C78)</f>
-        <v>257008</v>
-      </c>
-      <c r="H79" s="11">
-        <f>SUM(D69:D78)</f>
-        <v>168154</v>
-      </c>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" s="14">
+        <v>823537</v>
+      </c>
+      <c r="C79" s="14">
+        <v>28629</v>
+      </c>
+      <c r="D79" s="14">
+        <v>15520</v>
+      </c>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
       <c r="I79" s="3"/>
-      <c r="J79" s="11">
-        <f>ExtractedData[[#This Row],[чж NYY]]-F79</f>
-        <v>308700</v>
-      </c>
-      <c r="K79" s="11">
-        <f>ExtractedData[[#This Row],[чр YY]]-G79</f>
-        <v>298</v>
-      </c>
-      <c r="L79" s="11">
-        <f>ExtractedData[[#This Row],[чу YY]]-H79</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" t="s">
-        <v>83</v>
-      </c>
-      <c r="B80" s="3">
-        <v>63221</v>
-      </c>
-      <c r="C80" s="3" t="s">
+      <c r="J79" s="3"/>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3"/>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" s="14">
+        <v>677491</v>
+      </c>
+      <c r="C80" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="18" t="s">
         <v>75</v>
       </c>
       <c r="F80" s="3"/>
@@ -2541,37 +2592,55 @@
       <c r="L80" s="3"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" t="s">
-        <v>84</v>
-      </c>
-      <c r="B81" s="3">
-        <v>472811</v>
-      </c>
-      <c r="C81" s="3">
-        <v>23617</v>
-      </c>
-      <c r="D81" s="3">
-        <v>16764</v>
-      </c>
-      <c r="F81" s="3"/>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
+      <c r="A81" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81" s="20">
+        <v>7839177</v>
+      </c>
+      <c r="C81" s="17">
+        <v>257306</v>
+      </c>
+      <c r="D81" s="17">
+        <v>168154</v>
+      </c>
+      <c r="F81" s="9">
+        <f>SUM(B71:B80)</f>
+        <v>7530477</v>
+      </c>
+      <c r="G81" s="9">
+        <f>SUM(C71:C80)</f>
+        <v>257008</v>
+      </c>
+      <c r="H81" s="9">
+        <f>SUM(D71:D80)</f>
+        <v>168154</v>
+      </c>
       <c r="I81" s="3"/>
-      <c r="J81" s="3"/>
-      <c r="K81" s="3"/>
-      <c r="L81" s="3"/>
+      <c r="J81" s="9">
+        <f>ExtractedData[[#This Row],[чж NYY]]-F81</f>
+        <v>308700</v>
+      </c>
+      <c r="K81" s="9">
+        <f>ExtractedData[[#This Row],[чр YY]]-G81</f>
+        <v>298</v>
+      </c>
+      <c r="L81" s="9">
+        <f>ExtractedData[[#This Row],[чу YY]]-H81</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" t="s">
-        <v>85</v>
-      </c>
-      <c r="B82" s="3">
-        <v>545338</v>
-      </c>
-      <c r="C82" s="3" t="s">
+      <c r="A82" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82" s="14">
+        <v>63221</v>
+      </c>
+      <c r="C82" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="18" t="s">
         <v>75</v>
       </c>
       <c r="F82" s="3"/>
@@ -2583,17 +2652,17 @@
       <c r="L82" s="3"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" t="s">
-        <v>86</v>
-      </c>
-      <c r="B83" s="3">
-        <v>428962</v>
-      </c>
-      <c r="C83" s="3">
-        <v>20048</v>
-      </c>
-      <c r="D83" s="3">
-        <v>17313</v>
+      <c r="A83" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B83" s="14">
+        <v>472811</v>
+      </c>
+      <c r="C83" s="14">
+        <v>23617</v>
+      </c>
+      <c r="D83" s="14">
+        <v>16764</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
@@ -2604,16 +2673,16 @@
       <c r="L83" s="3"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" t="s">
-        <v>87</v>
-      </c>
-      <c r="B84" s="3">
-        <v>102786</v>
-      </c>
-      <c r="C84" s="3" t="s">
+      <c r="A84" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84" s="14">
+        <v>545338</v>
+      </c>
+      <c r="C84" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="18" t="s">
         <v>75</v>
       </c>
       <c r="F84" s="3"/>
@@ -2625,17 +2694,17 @@
       <c r="L84" s="3"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" t="s">
-        <v>88</v>
-      </c>
-      <c r="B85" s="3">
-        <v>1396310</v>
-      </c>
-      <c r="C85" s="3">
-        <v>72606</v>
-      </c>
-      <c r="D85" s="3">
-        <v>63817</v>
+      <c r="A85" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B85" s="14">
+        <v>428962</v>
+      </c>
+      <c r="C85" s="14">
+        <v>20048</v>
+      </c>
+      <c r="D85" s="14">
+        <v>17313</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
@@ -2646,17 +2715,17 @@
       <c r="L85" s="3"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" t="s">
-        <v>89</v>
-      </c>
-      <c r="B86" s="3">
-        <v>1328225</v>
-      </c>
-      <c r="C86" s="3">
-        <v>61076</v>
-      </c>
-      <c r="D86" s="3">
-        <v>33149</v>
+      <c r="A86" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B86" s="14">
+        <v>102786</v>
+      </c>
+      <c r="C86" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D86" s="18" t="s">
+        <v>75</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
@@ -2667,17 +2736,17 @@
       <c r="L86" s="3"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" t="s">
-        <v>90</v>
-      </c>
-      <c r="B87" s="3">
-        <v>256488</v>
-      </c>
-      <c r="C87" s="3">
-        <v>6239</v>
-      </c>
-      <c r="D87" s="3">
-        <v>5678</v>
+      <c r="A87" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B87" s="14">
+        <v>1396310</v>
+      </c>
+      <c r="C87" s="14">
+        <v>72606</v>
+      </c>
+      <c r="D87" s="14">
+        <v>63817</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
@@ -2688,56 +2757,38 @@
       <c r="L87" s="3"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B88" s="5">
-        <v>4609499</v>
-      </c>
-      <c r="C88" s="5">
-        <v>187046</v>
-      </c>
-      <c r="D88" s="5">
-        <v>141915</v>
-      </c>
-      <c r="F88" s="11">
-        <f>SUM(B80:B87)</f>
-        <v>4594141</v>
-      </c>
-      <c r="G88" s="11">
-        <f>SUM(C80:C87)</f>
-        <v>183586</v>
-      </c>
-      <c r="H88" s="11">
-        <f>SUM(D80:D87)</f>
-        <v>136721</v>
-      </c>
+      <c r="A88" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B88" s="14">
+        <v>1328225</v>
+      </c>
+      <c r="C88" s="14">
+        <v>61076</v>
+      </c>
+      <c r="D88" s="14">
+        <v>33149</v>
+      </c>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
       <c r="I88" s="3"/>
-      <c r="J88" s="11">
-        <f>ExtractedData[[#This Row],[чж NYY]]-F88</f>
-        <v>15358</v>
-      </c>
-      <c r="K88" s="11">
-        <f>ExtractedData[[#This Row],[чр YY]]-G88</f>
-        <v>3460</v>
-      </c>
-      <c r="L88" s="11">
-        <f>ExtractedData[[#This Row],[чу YY]]-H88</f>
-        <v>5194</v>
-      </c>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" t="s">
-        <v>92</v>
-      </c>
-      <c r="B89" s="3">
-        <v>485700</v>
-      </c>
-      <c r="C89" s="3">
-        <v>14594</v>
-      </c>
-      <c r="D89" s="3">
-        <v>10324</v>
+      <c r="A89" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B89" s="14">
+        <v>256488</v>
+      </c>
+      <c r="C89" s="14">
+        <v>6239</v>
+      </c>
+      <c r="D89" s="14">
+        <v>5678</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
@@ -2748,17 +2799,17 @@
       <c r="L89" s="3"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" t="s">
-        <v>93</v>
-      </c>
-      <c r="B90" s="3">
-        <v>695922</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>75</v>
+      <c r="A90" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B90" s="14">
+        <v>15358</v>
+      </c>
+      <c r="C90" s="14">
+        <v>460</v>
+      </c>
+      <c r="D90" s="14">
+        <v>194</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
@@ -2769,38 +2820,56 @@
       <c r="L90" s="3"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" t="s">
-        <v>94</v>
-      </c>
-      <c r="B91" s="3">
-        <v>703637</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
+      <c r="A91" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B91" s="17">
+        <v>4609499</v>
+      </c>
+      <c r="C91" s="17">
+        <v>187046</v>
+      </c>
+      <c r="D91" s="17">
+        <v>141915</v>
+      </c>
+      <c r="F91" s="9">
+        <f>SUM(B82:B90)</f>
+        <v>4609499</v>
+      </c>
+      <c r="G91" s="9">
+        <f>SUM(C82:C90)</f>
+        <v>184046</v>
+      </c>
+      <c r="H91" s="9">
+        <f>SUM(D82:D90)</f>
+        <v>136915</v>
+      </c>
       <c r="I91" s="3"/>
-      <c r="J91" s="3"/>
-      <c r="K91" s="3"/>
-      <c r="L91" s="3"/>
+      <c r="J91" s="9">
+        <f>ExtractedData[[#This Row],[чж NYY]]-F91</f>
+        <v>0</v>
+      </c>
+      <c r="K91" s="9">
+        <f>ExtractedData[[#This Row],[чр YY]]-G91</f>
+        <v>3000</v>
+      </c>
+      <c r="L91" s="9">
+        <f>ExtractedData[[#This Row],[чу YY]]-H91</f>
+        <v>5000</v>
+      </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" t="s">
-        <v>95</v>
-      </c>
-      <c r="B92" s="3">
-        <v>576578</v>
-      </c>
-      <c r="C92" s="3">
-        <v>10000</v>
-      </c>
-      <c r="D92" s="3">
-        <v>9753</v>
+      <c r="A92" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B92" s="14">
+        <v>485700</v>
+      </c>
+      <c r="C92" s="14">
+        <v>14594</v>
+      </c>
+      <c r="D92" s="14">
+        <v>10324</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
@@ -2811,17 +2880,17 @@
       <c r="L92" s="3"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" t="s">
-        <v>96</v>
-      </c>
-      <c r="B93" s="3">
-        <v>554205</v>
-      </c>
-      <c r="C93" s="3">
-        <v>16831</v>
-      </c>
-      <c r="D93" s="3">
-        <v>11969</v>
+      <c r="A93" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B93" s="14">
+        <v>695922</v>
+      </c>
+      <c r="C93" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D93" s="18" t="s">
+        <v>75</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
@@ -2832,16 +2901,16 @@
       <c r="L93" s="3"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" t="s">
-        <v>97</v>
-      </c>
-      <c r="B94" s="3">
-        <v>1188344</v>
-      </c>
-      <c r="C94" s="3" t="s">
+      <c r="A94" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B94" s="14">
+        <v>703637</v>
+      </c>
+      <c r="C94" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="18" t="s">
         <v>75</v>
       </c>
       <c r="F94" s="3"/>
@@ -2853,17 +2922,17 @@
       <c r="L94" s="3"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" t="s">
-        <v>98</v>
-      </c>
-      <c r="B95" s="3">
-        <v>351243</v>
-      </c>
-      <c r="C95" s="3">
-        <v>1523</v>
-      </c>
-      <c r="D95" s="3">
-        <v>842</v>
+      <c r="A95" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B95" s="14">
+        <v>576578</v>
+      </c>
+      <c r="C95" s="14">
+        <v>10000</v>
+      </c>
+      <c r="D95" s="14">
+        <v>9753</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
@@ -2874,17 +2943,17 @@
       <c r="L95" s="3"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96" t="s">
-        <v>99</v>
-      </c>
-      <c r="B96" s="3">
-        <v>547162</v>
-      </c>
-      <c r="C96" s="3">
-        <v>6921</v>
-      </c>
-      <c r="D96" s="3">
-        <v>4511</v>
+      <c r="A96" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B96" s="14">
+        <v>554205</v>
+      </c>
+      <c r="C96" s="14">
+        <v>16831</v>
+      </c>
+      <c r="D96" s="14">
+        <v>11969</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
@@ -2895,17 +2964,17 @@
       <c r="L96" s="3"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" t="s">
-        <v>100</v>
-      </c>
-      <c r="B97" s="3">
-        <v>815934</v>
-      </c>
-      <c r="C97" s="3">
-        <v>42533</v>
-      </c>
-      <c r="D97" s="3">
-        <v>27557</v>
+      <c r="A97" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B97" s="14">
+        <v>1188344</v>
+      </c>
+      <c r="C97" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D97" s="18" t="s">
+        <v>75</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
@@ -2916,81 +2985,144 @@
       <c r="L97" s="3"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98" s="14">
+        <v>351243</v>
+      </c>
+      <c r="C98" s="14">
+        <v>1523</v>
+      </c>
+      <c r="D98" s="14">
+        <v>842</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B99" s="14">
+        <v>547162</v>
+      </c>
+      <c r="C99" s="14">
+        <v>6921</v>
+      </c>
+      <c r="D99" s="14">
+        <v>4511</v>
+      </c>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3"/>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B100" s="14">
+        <v>815934</v>
+      </c>
+      <c r="C100" s="14">
+        <v>42533</v>
+      </c>
+      <c r="D100" s="14">
+        <v>27557</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="B98" s="5">
-        <v>5943725</v>
-      </c>
-      <c r="C98" s="5">
+      <c r="B101" s="17">
+        <v>5913725</v>
+      </c>
+      <c r="C101" s="17">
         <v>92949</v>
       </c>
-      <c r="D98" s="5">
+      <c r="D101" s="17">
         <v>64963</v>
       </c>
-      <c r="F98" s="11">
-        <f>SUM(B89:B97)</f>
+      <c r="F101" s="9">
+        <f>SUM(B92:B100)</f>
         <v>5918725</v>
       </c>
-      <c r="G98" s="11">
-        <f>SUM(C89:C97)</f>
+      <c r="G101" s="9">
+        <f>SUM(C92:C100)</f>
         <v>92402</v>
       </c>
-      <c r="H98" s="11">
-        <f>SUM(D89:D97)</f>
+      <c r="H101" s="9">
+        <f>SUM(D92:D100)</f>
         <v>64956</v>
       </c>
-      <c r="I98" s="3"/>
-      <c r="J98" s="11">
-        <f>ExtractedData[[#This Row],[чж NYY]]-F98</f>
-        <v>25000</v>
-      </c>
-      <c r="K98" s="11">
-        <f>ExtractedData[[#This Row],[чр YY]]-G98</f>
+      <c r="I101" s="3"/>
+      <c r="J101" s="9">
+        <f>ExtractedData[[#This Row],[чж NYY]]-F101</f>
+        <v>-5000</v>
+      </c>
+      <c r="K101" s="9">
+        <f>ExtractedData[[#This Row],[чр YY]]-G101</f>
         <v>547</v>
       </c>
-      <c r="L98" s="11">
-        <f>ExtractedData[[#This Row],[чу YY]]-H98</f>
+      <c r="L101" s="9">
+        <f>ExtractedData[[#This Row],[чу YY]]-H101</f>
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="4" t="s">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="B99" s="5">
+      <c r="B102" s="17">
         <v>112342758</v>
       </c>
-      <c r="C99" s="5">
+      <c r="C102" s="17">
         <v>5116996</v>
       </c>
-      <c r="D99" s="5">
+      <c r="D102" s="17">
         <v>3385518</v>
       </c>
-      <c r="F99" s="11">
-        <f>SUM(F68:F98)</f>
-        <v>109488126</v>
-      </c>
-      <c r="G99" s="11">
-        <f>SUM(G68:G98)</f>
-        <v>4991880</v>
-      </c>
-      <c r="H99" s="11">
-        <f>SUM(H68:H98)</f>
-        <v>3256921</v>
-      </c>
-      <c r="I99" s="3"/>
-      <c r="J99" s="11">
-        <f>ExtractedData[[#This Row],[чж NYY]]-F99</f>
-        <v>2854632</v>
-      </c>
-      <c r="K99" s="11">
-        <f>ExtractedData[[#This Row],[чр YY]]-G99</f>
-        <v>125116</v>
-      </c>
-      <c r="L99" s="11">
-        <f>ExtractedData[[#This Row],[чу YY]]-H99</f>
-        <v>128597</v>
+      <c r="F102" s="9">
+        <f>SUM(F70:F101)</f>
+        <v>109851387</v>
+      </c>
+      <c r="G102" s="9">
+        <f>SUM(G70:G101)</f>
+        <v>5006018</v>
+      </c>
+      <c r="H102" s="9">
+        <f>SUM(H70:H101)</f>
+        <v>3267047</v>
+      </c>
+      <c r="I102" s="3"/>
+      <c r="J102" s="9">
+        <f>ExtractedData[[#This Row],[чж NYY]]-F102</f>
+        <v>2491371</v>
+      </c>
+      <c r="K102" s="9">
+        <f>ExtractedData[[#This Row],[чр YY]]-G102</f>
+        <v>110978</v>
+      </c>
+      <c r="L102" s="9">
+        <f>ExtractedData[[#This Row],[чу YY]]-H102</f>
+        <v>118471</v>
       </c>
     </row>
   </sheetData>
@@ -3194,40 +3326,40 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="8">
         <v>2303602</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="8">
         <v>2303592</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="8">
         <v>10</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="8">
         <v>119051</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="8">
         <v>119051</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="8">
         <v>0</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="8">
         <v>80316</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="8">
         <v>80316</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="8">
         <v>0</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="7" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3442,36 +3574,36 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="8">
         <v>2500435</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10">
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8">
         <v>124380</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="8">
         <v>124400</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="8">
         <v>-20</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="8">
         <v>81485</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="8">
         <v>81583</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="8">
         <v>-98</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="K13" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="7" t="s">
         <v>118</v>
       </c>
     </row>
@@ -5797,6 +5929,309 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C32872C6-1AC7-4350-9FDD-4F3E12ABA86F}">
+  <dimension ref="A1:D40"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="13.68359375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="3">
+        <v>316471</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="3">
+        <v>202645</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="3">
+        <v>156193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="3">
+        <v>167709</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="3">
+        <v>178831</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="3">
+        <v>175635</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="3">
+        <v>177029</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="3">
+        <v>247202</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="3">
+        <v>167085</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="3">
+        <v>147720</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="3">
+        <v>201718</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="3">
+        <v>165354</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="3"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" s="3">
+        <f>SUM(B3:B14)</f>
+        <v>2303592</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="3">
+        <v>2303602</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="3">
+        <f>B17-B16</f>
+        <v>10</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="3">
+        <v>10194</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3">
+        <v>6425</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="3">
+        <v>16469</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3">
+        <v>10389</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="3">
+        <v>10583</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3">
+        <v>7820</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="3">
+        <v>9801</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3">
+        <v>6176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="3">
+        <v>10703</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3">
+        <v>6888</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="3">
+        <v>7116</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3">
+        <v>5183</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="3">
+        <v>8642</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3">
+        <v>6161</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="3">
+        <v>9256</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3">
+        <v>6546</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="3">
+        <v>9152</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3">
+        <v>6247</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="3">
+        <v>12204</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3">
+        <v>6598</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="3">
+        <v>9244</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3">
+        <v>6394</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="3">
+        <v>11036</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3">
+        <v>6756</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B35" s="3">
+        <f>SUM(B22:B33)</f>
+        <v>124400</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3">
+        <f>SUM(D22:D33)</f>
+        <v>81583</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" s="3">
+        <v>124380</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3">
+        <v>81485</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" s="3">
+        <f>B35-B36</f>
+        <v>20</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3">
+        <f>D35-D36</f>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1888.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1888.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06961BF-496A-4C13-ABB6-C0078BB334E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E2E60A-8580-4606-96DD-38F3ECE787D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="284">
   <si>
     <t>губ</t>
   </si>
@@ -1024,7 +1024,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1116,19 +1116,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1489,7 +1486,7 @@
       <c r="B21" s="34" t="s">
         <v>272</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="35" t="s">
         <v>273</v>
       </c>
       <c r="E21" s="3"/>
@@ -1541,7 +1538,7 @@
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="37" t="s">
         <v>274</v>
       </c>
     </row>
@@ -1615,7 +1612,7 @@
     <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="4.38671875" style="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" style="21" customWidth="1"/>
+    <col min="7" max="7" width="13.27734375" style="21" customWidth="1"/>
     <col min="8" max="8" width="5.609375" customWidth="1"/>
     <col min="9" max="23" width="7.27734375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="5.109375" customWidth="1"/>
@@ -1649,27 +1646,27 @@
       <c r="F1" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="36" t="s">
         <v>282</v>
       </c>
       <c r="H1" s="28"/>
-      <c r="I1" s="35" t="s">
+      <c r="I1" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
       <c r="Y1" s="29" t="s">
         <v>241</v>
       </c>
@@ -4372,15 +4369,15 @@
       </c>
       <c r="AB42" s="17"/>
       <c r="AC42" s="17">
-        <f>Y42-B42</f>
+        <f t="shared" ref="AC42:AE43" si="0">Y42-B42</f>
         <v>9990</v>
       </c>
       <c r="AD42" s="17">
-        <f>Z42-C42</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="AE42" s="17">
-        <f>AA42-D42</f>
+        <f t="shared" si="0"/>
         <v>98</v>
       </c>
       <c r="AG42" s="24">
@@ -4475,15 +4472,15 @@
       </c>
       <c r="AB43" s="4"/>
       <c r="AC43" s="4">
-        <f>Y43-B43</f>
+        <f t="shared" si="0"/>
         <v>1010</v>
       </c>
       <c r="AD43" s="4">
-        <f>Z43-C43</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE43" s="4">
-        <f>AA43-D43</f>
+        <f t="shared" si="0"/>
         <v>-90</v>
       </c>
       <c r="AG43" s="18">
@@ -4672,15 +4669,15 @@
       </c>
       <c r="AB46" s="4"/>
       <c r="AC46" s="4">
-        <f>Y46-B46</f>
+        <f t="shared" ref="AC46:AE47" si="1">Y46-B46</f>
         <v>0</v>
       </c>
       <c r="AD46" s="4">
-        <f>Z46-C46</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE46" s="4">
-        <f>AA46-D46</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG46" s="18">
@@ -4767,15 +4764,15 @@
       </c>
       <c r="AB47" s="4"/>
       <c r="AC47" s="4">
-        <f>Y47-B47</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD47" s="4">
-        <f>Z47-C47</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE47" s="4">
-        <f>AA47-D47</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG47" s="18">
@@ -7109,15 +7106,15 @@
       </c>
       <c r="AB83" s="17"/>
       <c r="AC83" s="17">
-        <f>Y83-B83</f>
+        <f t="shared" ref="AC83:AE84" si="2">Y83-B83</f>
         <v>60997</v>
       </c>
       <c r="AD83" s="17">
-        <f>Z83-C83</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE83" s="17">
-        <f>AA83-D83</f>
+        <f t="shared" si="2"/>
         <v>-60</v>
       </c>
       <c r="AG83" s="24">
@@ -7204,15 +7201,15 @@
       </c>
       <c r="AB84" s="4"/>
       <c r="AC84" s="4">
-        <f>Y84-B84</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD84" s="4">
-        <f>Z84-C84</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE84" s="4">
-        <f>AA84-D84</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG84" s="18">
@@ -9350,15 +9347,15 @@
       </c>
       <c r="AB114" s="4"/>
       <c r="AC114" s="4">
-        <f>Y114-B114</f>
+        <f t="shared" ref="AC114:AE115" si="3">Y114-B114</f>
         <v>0</v>
       </c>
       <c r="AD114" s="4">
-        <f>Z114-C114</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE114" s="4">
-        <f>AA114-D114</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG114" s="18">
@@ -9455,15 +9452,15 @@
       </c>
       <c r="AB115" s="4"/>
       <c r="AC115" s="4">
-        <f>Y115-B115</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD115" s="4">
-        <f>Z115-C115</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE115" s="4">
-        <f>AA115-D115</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG115" s="18">
@@ -11776,15 +11773,15 @@
       </c>
       <c r="AB148" s="4"/>
       <c r="AC148" s="4">
-        <f>Y148-B148</f>
+        <f t="shared" ref="AC148:AE149" si="4">Y148-B148</f>
         <v>0</v>
       </c>
       <c r="AD148" s="4">
-        <f>Z148-C148</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AE148" s="4">
-        <f>AA148-D148</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AG148" s="18">
@@ -11871,15 +11868,15 @@
       </c>
       <c r="AB149" s="4"/>
       <c r="AC149" s="4">
-        <f>Y149-B149</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AD149" s="4">
-        <f>Z149-C149</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AE149" s="4">
-        <f>AA149-D149</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AG149" s="18">
@@ -14069,28 +14066,28 @@
       <c r="W182" s="7"/>
       <c r="X182" s="3"/>
       <c r="Y182" s="4">
-        <f>B182</f>
+        <f t="shared" ref="Y182:AA183" si="5">B182</f>
         <v>73694</v>
       </c>
       <c r="Z182" s="4">
-        <f>C182</f>
+        <f t="shared" si="5"/>
         <v>3178</v>
       </c>
       <c r="AA182" s="4">
-        <f>D182</f>
+        <f t="shared" si="5"/>
         <v>2473</v>
       </c>
       <c r="AB182" s="4"/>
       <c r="AC182" s="4">
-        <f>Y182-B182</f>
+        <f t="shared" ref="AC182:AE184" si="6">Y182-B182</f>
         <v>0</v>
       </c>
       <c r="AD182" s="4">
-        <f>Z182-C182</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE182" s="4">
-        <f>AA182-D182</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG182" s="18">
@@ -14102,11 +14099,11 @@
         <v>33.557684479062068</v>
       </c>
       <c r="AJ182" s="18">
-        <f>AG182-E182</f>
+        <f t="shared" ref="AJ182:AK184" si="7">AG182-E182</f>
         <v>4.1242706326159535</v>
       </c>
       <c r="AK182" s="18">
-        <f>AH182-F182</f>
+        <f t="shared" si="7"/>
         <v>-0.24231552093792885</v>
       </c>
     </row>
@@ -14148,28 +14145,28 @@
       <c r="W183" s="7"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="4">
-        <f>B183</f>
+        <f t="shared" si="5"/>
         <v>274209</v>
       </c>
       <c r="Z183" s="4">
-        <f>C183</f>
+        <f t="shared" si="5"/>
         <v>10500</v>
       </c>
       <c r="AA183" s="4">
-        <f>D183</f>
+        <f t="shared" si="5"/>
         <v>7459</v>
       </c>
       <c r="AB183" s="4"/>
       <c r="AC183" s="4">
-        <f>Y183-B183</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD183" s="4">
-        <f>Z183-C183</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE183" s="4">
-        <f>AA183-D183</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG183" s="18">
@@ -14181,11 +14178,11 @@
         <v>27.20187885882666</v>
       </c>
       <c r="AJ183" s="18">
-        <f>AG183-E183</f>
+        <f t="shared" si="7"/>
         <v>-5.2080402174983291</v>
       </c>
       <c r="AK183" s="18">
-        <f>AH183-F183</f>
+        <f t="shared" si="7"/>
         <v>0.20187885882666023</v>
       </c>
     </row>
@@ -14270,15 +14267,15 @@
       </c>
       <c r="AB184" s="4"/>
       <c r="AC184" s="4">
-        <f>Y184-B184</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD184" s="4">
-        <f>Z184-C184</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE184" s="4">
-        <f>AA184-D184</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG184" s="18">
@@ -14290,11 +14287,11 @@
         <v>29.882006225302987</v>
       </c>
       <c r="AJ184" s="18">
-        <f>AG184-E184</f>
+        <f t="shared" si="7"/>
         <v>0.17362855692177703</v>
       </c>
       <c r="AK184" s="18">
-        <f>AH184-F184</f>
+        <f t="shared" si="7"/>
         <v>8.2006225302986735E-2</v>
       </c>
     </row>
@@ -14688,15 +14685,15 @@
       </c>
       <c r="AB190" s="17"/>
       <c r="AC190" s="17">
-        <f>Y190-B190</f>
+        <f t="shared" ref="AC190:AE193" si="8">Y190-B190</f>
         <v>-58032</v>
       </c>
       <c r="AD190" s="17">
-        <f>Z190-C190</f>
+        <f t="shared" si="8"/>
         <v>-565</v>
       </c>
       <c r="AE190" s="17">
-        <f>AA190-D190</f>
+        <f t="shared" si="8"/>
         <v>-1768</v>
       </c>
       <c r="AG190" s="24">
@@ -14708,11 +14705,11 @@
         <v>33.283926863223719</v>
       </c>
       <c r="AJ190" s="24">
-        <f>AG190-E190</f>
+        <f t="shared" ref="AJ190:AK193" si="9">AG190-E190</f>
         <v>1.1645591836497715E-3</v>
       </c>
       <c r="AK190" s="24">
-        <f>AH190-F190</f>
+        <f t="shared" si="9"/>
         <v>-1.6073136776277863E-2</v>
       </c>
     </row>
@@ -14767,15 +14764,15 @@
       </c>
       <c r="AB191" s="4"/>
       <c r="AC191" s="4">
-        <f>Y191-B191</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD191" s="4">
-        <f>Z191-C191</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE191" s="4">
-        <f>AA191-D191</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AG191" s="18">
@@ -14787,11 +14784,11 @@
         <v>34.179096795760636</v>
       </c>
       <c r="AJ191" s="18">
-        <f>AG191-E191</f>
+        <f t="shared" si="9"/>
         <v>15.350614843589554</v>
       </c>
       <c r="AK191" s="18">
-        <f>AH191-F191</f>
+        <f t="shared" si="9"/>
         <v>7.9096795760634109E-2</v>
       </c>
     </row>
@@ -14846,15 +14843,15 @@
       </c>
       <c r="AB192" s="17"/>
       <c r="AC192" s="17">
-        <f>Y192-B192</f>
+        <f t="shared" si="8"/>
         <v>-1949414</v>
       </c>
       <c r="AD192" s="17">
-        <f>Z192-C192</f>
+        <f t="shared" si="8"/>
         <v>-117822</v>
       </c>
       <c r="AE192" s="17">
-        <f>AA192-D192</f>
+        <f t="shared" si="8"/>
         <v>-68802</v>
       </c>
       <c r="AG192" s="24">
@@ -14866,11 +14863,11 @@
         <v>31.397980785829684</v>
       </c>
       <c r="AJ192" s="24">
-        <f>AG192-E192</f>
+        <f t="shared" si="9"/>
         <v>-2.9220466167139136E-2</v>
       </c>
       <c r="AK192" s="24">
-        <f>AH192-F192</f>
+        <f t="shared" si="9"/>
         <v>-2.0192141703141431E-3</v>
       </c>
     </row>
@@ -14939,15 +14936,15 @@
       </c>
       <c r="AB193" s="4"/>
       <c r="AC193" s="4">
-        <f>Y193-B193</f>
+        <f t="shared" si="8"/>
         <v>69400</v>
       </c>
       <c r="AD193" s="4">
-        <f>Z193-C193</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE193" s="4">
-        <f>AA193-D193</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AG193" s="18">
@@ -14959,11 +14956,11 @@
         <v>22.208309026030285</v>
       </c>
       <c r="AJ193" s="18">
-        <f>AG193-E193</f>
+        <f t="shared" si="9"/>
         <v>1.0987345962895745E-2</v>
       </c>
       <c r="AK193" s="18">
-        <f>AH193-F193</f>
+        <f t="shared" si="9"/>
         <v>8.3090260302860486E-3</v>
       </c>
     </row>
@@ -15116,15 +15113,15 @@
       </c>
       <c r="AB196" s="4"/>
       <c r="AC196" s="4">
-        <f>Y196-B196</f>
+        <f t="shared" ref="AC196:AE197" si="10">Y196-B196</f>
         <v>0</v>
       </c>
       <c r="AD196" s="4">
-        <f>Z196-C196</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AE196" s="4">
-        <f>AA196-D196</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AG196" s="18">
@@ -15211,15 +15208,15 @@
       </c>
       <c r="AB197" s="4"/>
       <c r="AC197" s="4">
-        <f>Y197-B197</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AD197" s="4">
-        <f>Z197-C197</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AE197" s="4">
-        <f>AA197-D197</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AG197" s="18">
@@ -15478,7 +15475,9 @@
       </c>
       <c r="E202" s="19"/>
       <c r="F202" s="19"/>
-      <c r="G202" s="19"/>
+      <c r="G202" s="1" t="s">
+        <v>194</v>
+      </c>
       <c r="H202" s="10"/>
       <c r="I202" s="7"/>
       <c r="J202" s="7"/>
@@ -16725,7 +16724,7 @@
       <c r="F222" s="22">
         <v>40.4</v>
       </c>
-      <c r="G222" s="37"/>
+      <c r="G222" s="19"/>
       <c r="H222" s="10"/>
       <c r="I222" s="6">
         <v>146461</v>
@@ -17378,28 +17377,28 @@
       <c r="W232" s="7"/>
       <c r="X232" s="3"/>
       <c r="Y232" s="4">
-        <f>B232</f>
+        <f t="shared" ref="Y232:AA233" si="11">B232</f>
         <v>256488</v>
       </c>
       <c r="Z232" s="4">
-        <f>C232</f>
+        <f t="shared" si="11"/>
         <v>6239</v>
       </c>
       <c r="AA232" s="4">
-        <f>D232</f>
+        <f t="shared" si="11"/>
         <v>5678</v>
       </c>
       <c r="AB232" s="4"/>
       <c r="AC232" s="4">
-        <f>Y232-B232</f>
+        <f t="shared" ref="AC232:AE234" si="12">Y232-B232</f>
         <v>0</v>
       </c>
       <c r="AD232" s="4">
-        <f>Z232-C232</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AE232" s="4">
-        <f>AA232-D232</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AG232" s="18">
@@ -17411,11 +17410,11 @@
         <v>22.137487913664575</v>
       </c>
       <c r="AJ232" s="18">
-        <f>AG232-E232</f>
+        <f t="shared" ref="AJ232:AK235" si="13">AG232-E232</f>
         <v>2.4724743457781528E-2</v>
       </c>
       <c r="AK232" s="18">
-        <f>AH232-F232</f>
+        <f t="shared" si="13"/>
         <v>3.7487913664573824E-2</v>
       </c>
     </row>
@@ -17457,28 +17456,28 @@
       <c r="W233" s="7"/>
       <c r="X233" s="3"/>
       <c r="Y233" s="4">
-        <f>B233</f>
+        <f t="shared" si="11"/>
         <v>15358</v>
       </c>
       <c r="Z233" s="4">
-        <f>C233</f>
+        <f t="shared" si="11"/>
         <v>460</v>
       </c>
       <c r="AA233" s="4">
-        <f>D233</f>
+        <f t="shared" si="11"/>
         <v>194</v>
       </c>
       <c r="AB233" s="4"/>
       <c r="AC233" s="4">
-        <f>Y233-B233</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AD233" s="4">
-        <f>Z233-C233</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AE233" s="4">
-        <f>AA233-D233</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AG233" s="18">
@@ -17490,11 +17489,11 @@
         <v>12.63185310587316</v>
       </c>
       <c r="AJ233" s="18">
-        <f>AG233-E233</f>
+        <f t="shared" si="13"/>
         <v>-0.64818335720796938</v>
       </c>
       <c r="AK233" s="18">
-        <f>AH233-F233</f>
+        <f t="shared" si="13"/>
         <v>-0.2681468941268399</v>
       </c>
     </row>
@@ -17549,15 +17548,15 @@
       </c>
       <c r="AB234" s="17"/>
       <c r="AC234" s="17">
-        <f>Y234-B234</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AD234" s="17">
-        <f>Z234-C234</f>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="AE234" s="17">
-        <f>AA234-D234</f>
+        <f t="shared" si="12"/>
         <v>-1000</v>
       </c>
       <c r="AG234" s="24">
@@ -17569,11 +17568,11 @@
         <v>30.787510746829536</v>
       </c>
       <c r="AJ234" s="24">
-        <f>AG234-E234</f>
+        <f t="shared" si="13"/>
         <v>-7.4216204407463806</v>
       </c>
       <c r="AK234" s="24">
-        <f>AH234-F234</f>
+        <f t="shared" si="13"/>
         <v>-5.6124892531704624</v>
       </c>
     </row>
@@ -17639,11 +17638,11 @@
         <v>21.255919291743872</v>
       </c>
       <c r="AJ235" s="18">
-        <f>AG235-E235</f>
+        <f t="shared" si="13"/>
         <v>4.1177681696520807E-2</v>
       </c>
       <c r="AK235" s="18">
-        <f>AH235-F235</f>
+        <f t="shared" si="13"/>
         <v>5.591929174387289E-2</v>
       </c>
     </row>
@@ -17685,15 +17684,15 @@
       <c r="W236" s="7"/>
       <c r="X236" s="3"/>
       <c r="Y236" s="4">
-        <f t="shared" ref="Y236:Y243" si="0">B236</f>
+        <f t="shared" ref="Y236:Y243" si="14">B236</f>
         <v>695922</v>
       </c>
       <c r="Z236" s="25" t="str">
-        <f t="shared" ref="Z236:Z243" si="1">C236</f>
+        <f t="shared" ref="Z236:Z243" si="15">C236</f>
         <v>—</v>
       </c>
       <c r="AA236" s="25" t="str">
-        <f t="shared" ref="AA236:AA243" si="2">D236</f>
+        <f t="shared" ref="AA236:AA243" si="16">D236</f>
         <v>—</v>
       </c>
       <c r="AB236" s="4"/>
@@ -17743,15 +17742,15 @@
       <c r="W237" s="7"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>703637</v>
       </c>
       <c r="Z237" s="25" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="15"/>
         <v>—</v>
       </c>
       <c r="AA237" s="25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="16"/>
         <v>—</v>
       </c>
       <c r="AB237" s="4"/>
@@ -17801,15 +17800,15 @@
       <c r="W238" s="7"/>
       <c r="X238" s="3"/>
       <c r="Y238" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>576578</v>
       </c>
       <c r="Z238" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="15"/>
         <v>10000</v>
       </c>
       <c r="AA238" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="16"/>
         <v>9753</v>
       </c>
       <c r="AB238" s="4"/>
@@ -17871,15 +17870,15 @@
       <c r="W239" s="7"/>
       <c r="X239" s="3"/>
       <c r="Y239" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>554205</v>
       </c>
       <c r="Z239" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="15"/>
         <v>16381</v>
       </c>
       <c r="AA239" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="16"/>
         <v>11969</v>
       </c>
       <c r="AB239" s="4"/>
@@ -17941,15 +17940,15 @@
       <c r="W240" s="7"/>
       <c r="X240" s="3"/>
       <c r="Y240" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>1183344</v>
       </c>
       <c r="Z240" s="25" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="15"/>
         <v>—</v>
       </c>
       <c r="AA240" s="25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="16"/>
         <v>—</v>
       </c>
       <c r="AB240" s="4"/>
@@ -17999,15 +17998,15 @@
       <c r="W241" s="7"/>
       <c r="X241" s="3"/>
       <c r="Y241" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>351243</v>
       </c>
       <c r="Z241" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="15"/>
         <v>1523</v>
       </c>
       <c r="AA241" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="16"/>
         <v>842</v>
       </c>
       <c r="AB241" s="4"/>
@@ -18063,15 +18062,15 @@
       <c r="W242" s="7"/>
       <c r="X242" s="3"/>
       <c r="Y242" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>547162</v>
       </c>
       <c r="Z242" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="15"/>
         <v>6921</v>
       </c>
       <c r="AA242" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="16"/>
         <v>4511</v>
       </c>
       <c r="AB242" s="4"/>
@@ -18130,15 +18129,15 @@
       <c r="W243" s="7"/>
       <c r="X243" s="3"/>
       <c r="Y243" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>815934</v>
       </c>
       <c r="Z243" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="15"/>
         <v>42533</v>
       </c>
       <c r="AA243" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="16"/>
         <v>27557</v>
       </c>
       <c r="AB243" s="4"/>
@@ -18213,15 +18212,15 @@
       </c>
       <c r="AB244" s="17"/>
       <c r="AC244" s="17">
-        <f>Y244-B244</f>
+        <f t="shared" ref="AC244:AE245" si="17">Y244-B244</f>
         <v>0</v>
       </c>
       <c r="AD244" s="17">
-        <f>Z244-C244</f>
+        <f t="shared" si="17"/>
         <v>-1000</v>
       </c>
       <c r="AE244" s="17">
-        <f>AA244-D244</f>
+        <f t="shared" si="17"/>
         <v>-7</v>
       </c>
       <c r="AG244" s="24">
@@ -18292,15 +18291,15 @@
       </c>
       <c r="AB245" s="17"/>
       <c r="AC245" s="17">
-        <f>Y245-B245</f>
+        <f t="shared" si="17"/>
         <v>-2562952</v>
       </c>
       <c r="AD245" s="17">
-        <f>Z245-C245</f>
+        <f t="shared" si="17"/>
         <v>-139682</v>
       </c>
       <c r="AE245" s="17">
-        <f>AA245-D245</f>
+        <f t="shared" si="17"/>
         <v>-85966</v>
       </c>
       <c r="AG245" s="24">

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1888.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1888.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E2E60A-8580-4606-96DD-38F3ECE787D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAF3986-DCC9-490D-8B6D-EC65077C6253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -14720,8 +14720,8 @@
       <c r="B191" s="5">
         <v>1962369</v>
       </c>
-      <c r="C191" s="5">
-        <v>147277</v>
+      <c r="C191" s="32">
+        <v>117277</v>
       </c>
       <c r="D191" s="5">
         <v>67072</v>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="Z191" s="4">
         <f>C191</f>
-        <v>147277</v>
+        <v>117277</v>
       </c>
       <c r="AA191" s="4">
         <f>D191</f>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="AG191" s="18">
         <f>C191/B191*1000</f>
-        <v>75.050614843589557</v>
+        <v>59.762970165142235</v>
       </c>
       <c r="AH191" s="18">
         <f>D191/B191*1000</f>
@@ -14785,7 +14785,7 @@
       </c>
       <c r="AJ191" s="18">
         <f t="shared" si="9"/>
-        <v>15.350614843589554</v>
+        <v>6.2970165142232304E-2</v>
       </c>
       <c r="AK191" s="18">
         <f t="shared" si="9"/>
